--- a/output/summary_tables/WIETS Imports Module Summary Tables.xlsx
+++ b/output/summary_tables/WIETS Imports Module Summary Tables.xlsx
@@ -453,7 +453,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="28.5"/>
@@ -468,7 +468,7 @@
       <c r="A1" s="7" t="inlineStr">
         <is>
           <t>WIETS (Waste Import Export Tracking System) Imports - notices for bringing hazardous waste into the U.S.
-Distinct facilities are U.S. importers.</t>
+Distinct facilities are U.S. importers. Summarized from the WT_IMPORTS_MASTER master file.</t>
         </is>
       </c>
       <c r="B1" s="7"/>
@@ -480,7 +480,7 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Identifier: IMPORTER_EPA_ID, one row per import-notice consent / waste stream.</t>
+          <t>Identifier: IMPORTER_EPA_ID, one row per import-notice waste stream.</t>
         </is>
       </c>
       <c r="B2" s="7"/>
@@ -533,7 +533,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>30 other columns not summarized (identifiers, names, and descriptions / free-text fields).</t>
+          <t>20 other columns are not summarized because they hold record identifiers, personal names and staff identifiers, correspondence addresses and contact details, free-text notes, or the description text paired with a code that is summarized here. They are named below the table.</t>
         </is>
       </c>
       <c r="C5" s="7"/>
@@ -582,6 +582,92 @@
               <color rgb="FF000000"/>
               <rFont val="Calibri"/>
             </rPr>
+            <t xml:space="preserve">NOTICE_TYPE
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>Direction of the notice; every row of this master is an import.</t>
+          </r>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>0%
+(0)</t>
+        </is>
+      </c>
+      <c r="C7" s="11">
+        <v>1</v>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>Import</t>
+        </is>
+      </c>
+      <c r="E7" s="12">
+        <v>100</v>
+      </c>
+      <c r="F7" s="10">
+        <v>72230</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">NOTICE_PROGRESS
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>How far the notice has moved through EPA's review.</t>
+          </r>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>0%
+(0)</t>
+        </is>
+      </c>
+      <c r="C8" s="11">
+        <v>1</v>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="E8" s="12">
+        <v>100</v>
+      </c>
+      <c r="F8" s="10">
+        <v>72230</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
             <t xml:space="preserve">NOTICE_STATUS
 </t>
           </r>
@@ -595,100 +681,41 @@
           </r>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>0%
 (0)</t>
         </is>
       </c>
-      <c r="C7" s="11">
+      <c r="C9" s="11">
         <v>3</v>
       </c>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>DeterminationMade</t>
         </is>
       </c>
-      <c r="E7" s="12">
+      <c r="E9" s="12">
         <v>99.8</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F9" s="10">
         <v>72073</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="10"/>
-      <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="10" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="10"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>Withdrawn</t>
         </is>
       </c>
-      <c r="E8" s="12">
+      <c r="E10" s="12">
         <v>0.2</v>
       </c>
-      <c r="F8" s="10">
+      <c r="F10" s="10">
         <v>111</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="10"/>
-      <c r="B9" s="11"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="10" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="E9" s="12">
-        <v>0.1</v>
-      </c>
-      <c r="F9" s="10">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <sz val="12"/>
-              <color rgb="FF000000"/>
-              <rFont val="Calibri"/>
-            </rPr>
-            <t xml:space="preserve">DETERMINATION
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="12"/>
-              <color rgb="FF666666"/>
-              <rFont val="Calibri"/>
-            </rPr>
-            <t>EPA consent determination on the notice.</t>
-          </r>
-        </is>
-      </c>
-      <c r="B10" s="11" t="inlineStr">
-        <is>
-          <t>0.1%
-(46)</t>
-        </is>
-      </c>
-      <c r="C10" s="11">
-        <v>4</v>
-      </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>Consent</t>
-        </is>
-      </c>
-      <c r="E10" s="12">
-        <v>86.8</v>
-      </c>
-      <c r="F10" s="10">
-        <v>62663</v>
       </c>
     </row>
     <row r="11">
@@ -697,30 +724,57 @@
       <c r="C11" s="11"/>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>ConditionalConsent</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E11" s="12">
-        <v>10.4</v>
+        <v>0.1</v>
       </c>
       <c r="F11" s="10">
-        <v>7521</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">DETERMINATION
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>EPA consent determination on the notice.</t>
+          </r>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>0.1%
+(46)</t>
+        </is>
+      </c>
+      <c r="C12" s="11">
+        <v>4</v>
+      </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>NeitherConsentNorObject</t>
+          <t>Consent</t>
         </is>
       </c>
       <c r="E12" s="12">
-        <v>1.5</v>
+        <v>86.8</v>
       </c>
       <c r="F12" s="10">
-        <v>1073</v>
+        <v>62663</v>
       </c>
     </row>
     <row r="13">
@@ -729,57 +783,30 @@
       <c r="C13" s="11"/>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>Object</t>
+          <t>ConditionalConsent</t>
         </is>
       </c>
       <c r="E13" s="12">
-        <v>1.3</v>
+        <v>10.4</v>
       </c>
       <c r="F13" s="10">
-        <v>927</v>
+        <v>7521</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <sz val="12"/>
-              <color rgb="FF000000"/>
-              <rFont val="Calibri"/>
-            </rPr>
-            <t xml:space="preserve">EXPORTER_COUNTRY
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="12"/>
-              <color rgb="FF666666"/>
-              <rFont val="Calibri"/>
-            </rPr>
-            <t>Country of the exporter (origin).</t>
-          </r>
-        </is>
-      </c>
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t>0%
-(0)</t>
-        </is>
-      </c>
-      <c r="C14" s="11">
-        <v>36</v>
-      </c>
+      <c r="A14" s="10"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>NeitherConsentNorObject</t>
         </is>
       </c>
       <c r="E14" s="12">
-        <v>95.1</v>
+        <v>1.5</v>
       </c>
       <c r="F14" s="10">
-        <v>68665</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="15">
@@ -788,30 +815,57 @@
       <c r="C15" s="11"/>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="E15" s="12">
-        <v>4.4</v>
+        <v>1.3</v>
       </c>
       <c r="F15" s="10">
-        <v>3201</v>
+        <v>927</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="10"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">CONSENT_UOM
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>Unit of measure the consented quantity is stated in.</t>
+          </r>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>1.3%
+(973)</t>
+        </is>
+      </c>
+      <c r="C16" s="11">
+        <v>3</v>
+      </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>Grenada</t>
+          <t>Kilograms</t>
         </is>
       </c>
       <c r="E16" s="12">
-        <v>0.1</v>
+        <v>92.3</v>
       </c>
       <c r="F16" s="10">
-        <v>90</v>
+        <v>66660</v>
       </c>
     </row>
     <row r="17">
@@ -820,14 +874,14 @@
       <c r="C17" s="11"/>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Litres</t>
         </is>
       </c>
       <c r="E17" s="12">
-        <v>0.1</v>
+        <v>6.1</v>
       </c>
       <c r="F17" s="10">
-        <v>80</v>
+        <v>4427</v>
       </c>
     </row>
     <row r="18">
@@ -836,73 +890,73 @@
       <c r="C18" s="11"/>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>Bahamas</t>
+          <t>Metric Tons</t>
         </is>
       </c>
       <c r="E18" s="12">
+        <v>0.2</v>
+      </c>
+      <c r="F18" s="10">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">CONSENT_FREQUENCY
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>Frequency of consented shipments.</t>
+          </r>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>1.3%
+(973)</t>
+        </is>
+      </c>
+      <c r="C19" s="11">
+        <v>3</v>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>Annually</t>
+        </is>
+      </c>
+      <c r="E19" s="12">
+        <v>98.6</v>
+      </c>
+      <c r="F19" s="10">
+        <v>71244</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="E20" s="12">
         <v>0</v>
       </c>
-      <c r="F18" s="10">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="10"/>
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="10" t="inlineStr">
-        <is>
-          <t>All Other (31)</t>
-        </is>
-      </c>
-      <c r="E19" s="12">
-        <v>0.2</v>
-      </c>
-      <c r="F19" s="10">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <sz val="12"/>
-              <color rgb="FF000000"/>
-              <rFont val="Calibri"/>
-            </rPr>
-            <t xml:space="preserve">FINAL_COUNTRY
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="12"/>
-              <color rgb="FF666666"/>
-              <rFont val="Calibri"/>
-            </rPr>
-            <t>Country of the final recovery / disposal facility.</t>
-          </r>
-        </is>
-      </c>
-      <c r="B20" s="11" t="inlineStr">
-        <is>
-          <t>0%
-(0)</t>
-        </is>
-      </c>
-      <c r="C20" s="11">
-        <v>6</v>
-      </c>
-      <c r="D20" s="10" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E20" s="12">
-        <v>100</v>
-      </c>
       <c r="F20" s="10">
-        <v>72195</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21">
@@ -911,30 +965,57 @@
       <c r="C21" s="11"/>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="E21" s="12">
         <v>0</v>
       </c>
       <c r="F21" s="10">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="10"/>
-      <c r="B22" s="11"/>
-      <c r="C22" s="11"/>
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">EXPORTER_COUNTRY
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>Country of the exporter (origin).</t>
+          </r>
+        </is>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>0%
+(0)</t>
+        </is>
+      </c>
+      <c r="C22" s="11">
+        <v>36</v>
+      </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>Korea, Republic Of (South Korea)</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="E22" s="12">
-        <v>0</v>
+        <v>95.1</v>
       </c>
       <c r="F22" s="10">
-        <v>9</v>
+        <v>68665</v>
       </c>
     </row>
     <row r="23">
@@ -943,14 +1024,14 @@
       <c r="C23" s="11"/>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="E23" s="12">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="F23" s="10">
-        <v>8</v>
+        <v>3201</v>
       </c>
     </row>
     <row r="24">
@@ -959,14 +1040,14 @@
       <c r="C24" s="11"/>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Grenada</t>
         </is>
       </c>
       <c r="E24" s="12">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F24" s="10">
-        <v>1</v>
+        <v>90</v>
       </c>
     </row>
     <row r="25">
@@ -975,57 +1056,30 @@
       <c r="C25" s="11"/>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E25" s="12">
+        <v>0.1</v>
+      </c>
+      <c r="F25" s="10">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="10" t="inlineStr">
+        <is>
+          <t>Bahamas</t>
+        </is>
+      </c>
+      <c r="E26" s="12">
         <v>0</v>
       </c>
-      <c r="F25" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <sz val="12"/>
-              <color rgb="FF000000"/>
-              <rFont val="Calibri"/>
-            </rPr>
-            <t xml:space="preserve">FINAL_OPERATIONS
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="12"/>
-              <color rgb="FF666666"/>
-              <rFont val="Calibri"/>
-            </rPr>
-            <t>Basel recovery (R) or disposal (D) operation at the final facility.</t>
-          </r>
-        </is>
-      </c>
-      <c r="B26" s="11" t="inlineStr">
-        <is>
-          <t>0.1%
-(40)</t>
-        </is>
-      </c>
-      <c r="C26" s="11">
-        <v>27</v>
-      </c>
-      <c r="D26" s="10" t="inlineStr">
-        <is>
-          <t>D10 - Incineration On Land</t>
-        </is>
-      </c>
-      <c r="E26" s="12">
-        <v>83.6</v>
-      </c>
       <c r="F26" s="10">
-        <v>60387</v>
+        <v>35</v>
       </c>
     </row>
     <row r="27">
@@ -1034,30 +1088,57 @@
       <c r="C27" s="11"/>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>D9 - Physico-Chemical Treatment</t>
+          <t>All Other (31)</t>
         </is>
       </c>
       <c r="E27" s="12">
-        <v>7.5</v>
+        <v>0.2</v>
       </c>
       <c r="F27" s="10">
-        <v>5387</v>
+        <v>159</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="10"/>
-      <c r="B28" s="11"/>
-      <c r="C28" s="11"/>
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">SHIPPER_COUNTRY
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>Country of the shipper that sends the waste.</t>
+          </r>
+        </is>
+      </c>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>1.4%
+(1001)</t>
+        </is>
+      </c>
+      <c r="C28" s="11">
+        <v>33</v>
+      </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>R4 - Recycling/Reclamation Of Metals</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="E28" s="12">
-        <v>4.1</v>
+        <v>95.1</v>
       </c>
       <c r="F28" s="10">
-        <v>2966</v>
+        <v>68665</v>
       </c>
     </row>
     <row r="29">
@@ -1066,14 +1147,14 @@
       <c r="C29" s="11"/>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>D3 - Deep Injection</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="E29" s="12">
-        <v>1.4</v>
+        <v>3.1</v>
       </c>
       <c r="F29" s="10">
-        <v>1018</v>
+        <v>2210</v>
       </c>
     </row>
     <row r="30">
@@ -1082,14 +1163,14 @@
       <c r="C30" s="11"/>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>RC1</t>
+          <t>Grenada</t>
         </is>
       </c>
       <c r="E30" s="12">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
       <c r="F30" s="10">
-        <v>596</v>
+        <v>90</v>
       </c>
     </row>
     <row r="31">
@@ -1098,57 +1179,30 @@
       <c r="C31" s="11"/>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>All Other (22)</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E31" s="12">
-        <v>2.5</v>
+        <v>0.1</v>
       </c>
       <c r="F31" s="10">
-        <v>1836</v>
+        <v>73</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <sz val="12"/>
-              <color rgb="FF000000"/>
-              <rFont val="Calibri"/>
-            </rPr>
-            <t xml:space="preserve">WS_WASTE_TYPE
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="12"/>
-              <color rgb="FF666666"/>
-              <rFont val="Calibri"/>
-            </rPr>
-            <t>Waste-stream type.</t>
-          </r>
-        </is>
-      </c>
-      <c r="B32" s="11" t="inlineStr">
-        <is>
-          <t>0.1%
-(40)</t>
-        </is>
-      </c>
-      <c r="C32" s="11">
-        <v>8</v>
-      </c>
+      <c r="A32" s="10"/>
+      <c r="B32" s="11"/>
+      <c r="C32" s="11"/>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>UNC</t>
+          <t>Bahamas</t>
         </is>
       </c>
       <c r="E32" s="12">
-        <v>95.8</v>
+        <v>0</v>
       </c>
       <c r="F32" s="10">
-        <v>69225</v>
+        <v>35</v>
       </c>
     </row>
     <row r="33">
@@ -1157,46 +1211,100 @@
       <c r="C33" s="11"/>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>HAZ - Hazardous Waste</t>
+          <t>All Other (28)</t>
         </is>
       </c>
       <c r="E33" s="12">
-        <v>3.4</v>
+        <v>0.2</v>
       </c>
       <c r="F33" s="10">
-        <v>2424</v>
+        <v>156</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="10"/>
-      <c r="B34" s="11"/>
-      <c r="C34" s="11"/>
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">INTERIM_COUNTRY
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>Country of the interim facility, where the shipment passes through one.</t>
+          </r>
+        </is>
+      </c>
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t>90.7%
+(65519)</t>
+        </is>
+      </c>
+      <c r="C34" s="11">
+        <v>1</v>
+      </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>UNIV - Universal Waste</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E34" s="12">
-        <v>0.5</v>
+        <v>9.3</v>
       </c>
       <c r="F34" s="10">
-        <v>394</v>
+        <v>6711</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="10"/>
-      <c r="B35" s="11"/>
-      <c r="C35" s="11"/>
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">INTERIM_OPERATIONS
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>Basel recovery (R) or disposal (D) operation at the interim facility.</t>
+          </r>
+        </is>
+      </c>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>90.7%
+(65533)</t>
+        </is>
+      </c>
+      <c r="C35" s="11">
+        <v>7</v>
+      </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>SLABS - Spent Lead-Acid Batteries</t>
+          <t>D15 - Storage Pending Disposal</t>
         </is>
       </c>
       <c r="E35" s="12">
-        <v>0.1</v>
+        <v>5.8</v>
       </c>
       <c r="F35" s="10">
-        <v>108</v>
+        <v>4199</v>
       </c>
     </row>
     <row r="36">
@@ -1205,14 +1313,14 @@
       <c r="C36" s="11"/>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>MIXED - Mixed Waste</t>
+          <t>R13 - Storage Pending Recovery</t>
         </is>
       </c>
       <c r="E36" s="12">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="F36" s="10">
-        <v>13</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="37">
@@ -1221,57 +1329,30 @@
       <c r="C37" s="11"/>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>All Other (3)</t>
+          <t>D13 - Blending Prior To Disposal</t>
         </is>
       </c>
       <c r="E37" s="12">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="F37" s="10">
-        <v>26</v>
+        <v>828</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <sz val="12"/>
-              <color rgb="FF000000"/>
-              <rFont val="Calibri"/>
-            </rPr>
-            <t xml:space="preserve">HAZARD_CLASS
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="12"/>
-              <color rgb="FF666666"/>
-              <rFont val="Calibri"/>
-            </rPr>
-            <t>UN / DOT hazard class of the waste.</t>
-          </r>
-        </is>
-      </c>
-      <c r="B38" s="11" t="inlineStr">
-        <is>
-          <t>0.2%
-(156)</t>
-        </is>
-      </c>
-      <c r="C38" s="11">
-        <v>19</v>
-      </c>
+      <c r="A38" s="10"/>
+      <c r="B38" s="11"/>
+      <c r="C38" s="11"/>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t>8 - Corrosive</t>
+          <t>D14 - Repackaging Prior To Disposal</t>
         </is>
       </c>
       <c r="E38" s="12">
-        <v>21.7</v>
+        <v>0.3</v>
       </c>
       <c r="F38" s="10">
-        <v>15701</v>
+        <v>193</v>
       </c>
     </row>
     <row r="39">
@@ -1280,14 +1361,14 @@
       <c r="C39" s="11"/>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>6.1 - Toxic</t>
+          <t>D14; D15</t>
         </is>
       </c>
       <c r="E39" s="12">
-        <v>16.7</v>
+        <v>0.2</v>
       </c>
       <c r="F39" s="10">
-        <v>12059</v>
+        <v>120</v>
       </c>
     </row>
     <row r="40">
@@ -1296,30 +1377,57 @@
       <c r="C40" s="11"/>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>3 - Flammable Liquid</t>
+          <t>All Other (2)</t>
         </is>
       </c>
       <c r="E40" s="12">
-        <v>14.6</v>
+        <v>0.1</v>
       </c>
       <c r="F40" s="10">
-        <v>10564</v>
+        <v>60</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="10"/>
-      <c r="B41" s="11"/>
-      <c r="C41" s="11"/>
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">FINAL_COUNTRY
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>Country of the final recovery / disposal facility.</t>
+          </r>
+        </is>
+      </c>
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>0%
+(0)</t>
+        </is>
+      </c>
+      <c r="C41" s="11">
+        <v>6</v>
+      </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>9 - Miscellaneous Dangerous Goods</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E41" s="12">
-        <v>6.8</v>
+        <v>100</v>
       </c>
       <c r="F41" s="10">
-        <v>4917</v>
+        <v>72195</v>
       </c>
     </row>
     <row r="42">
@@ -1328,14 +1436,14 @@
       <c r="C42" s="11"/>
       <c r="D42" s="10" t="inlineStr">
         <is>
-          <t>4.3 - Dangerous When Wet</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="E42" s="12">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="F42" s="10">
-        <v>4541</v>
+        <v>16</v>
       </c>
     </row>
     <row r="43">
@@ -1344,57 +1452,30 @@
       <c r="C43" s="11"/>
       <c r="D43" s="10" t="inlineStr">
         <is>
-          <t>All Other (14)</t>
+          <t>Korea, Republic Of (South Korea)</t>
         </is>
       </c>
       <c r="E43" s="12">
-        <v>33.6</v>
+        <v>0</v>
       </c>
       <c r="F43" s="10">
-        <v>24292</v>
+        <v>9</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <sz val="12"/>
-              <color rgb="FF000000"/>
-              <rFont val="Calibri"/>
-            </rPr>
-            <t xml:space="preserve">CONSENT_FREQUENCY
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="12"/>
-              <color rgb="FF666666"/>
-              <rFont val="Calibri"/>
-            </rPr>
-            <t>Frequency of consented shipments.</t>
-          </r>
-        </is>
-      </c>
-      <c r="B44" s="11" t="inlineStr">
-        <is>
-          <t>1.3%
-(973)</t>
-        </is>
-      </c>
-      <c r="C44" s="11">
-        <v>3</v>
-      </c>
+      <c r="A44" s="10"/>
+      <c r="B44" s="11"/>
+      <c r="C44" s="11"/>
       <c r="D44" s="10" t="inlineStr">
         <is>
-          <t>Annually</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="E44" s="12">
-        <v>98.6</v>
+        <v>0</v>
       </c>
       <c r="F44" s="10">
-        <v>71244</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45">
@@ -1403,14 +1484,14 @@
       <c r="C45" s="11"/>
       <c r="D45" s="10" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="E45" s="12">
         <v>0</v>
       </c>
       <c r="F45" s="10">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -1419,132 +1500,901 @@
       <c r="C46" s="11"/>
       <c r="D46" s="10" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="E46" s="12">
         <v>0</v>
       </c>
       <c r="F46" s="10">
-        <v>6</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">FINAL_OPERATIONS
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>Basel recovery (R) or disposal (D) operation at the final facility.</t>
+          </r>
+        </is>
+      </c>
+      <c r="B47" s="11" t="inlineStr">
+        <is>
+          <t>0.1%
+(40)</t>
+        </is>
+      </c>
+      <c r="C47" s="11">
+        <v>27</v>
+      </c>
+      <c r="D47" s="10" t="inlineStr">
+        <is>
+          <t>D10 - Incineration On Land</t>
+        </is>
+      </c>
+      <c r="E47" s="12">
+        <v>83.6</v>
+      </c>
+      <c r="F47" s="10">
+        <v>60387</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="14" t="inlineStr">
+      <c r="A48" s="10"/>
+      <c r="B48" s="11"/>
+      <c r="C48" s="11"/>
+      <c r="D48" s="10" t="inlineStr">
+        <is>
+          <t>D9 - Physico-Chemical Treatment</t>
+        </is>
+      </c>
+      <c r="E48" s="12">
+        <v>7.5</v>
+      </c>
+      <c r="F48" s="10">
+        <v>5387</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="10"/>
+      <c r="B49" s="11"/>
+      <c r="C49" s="11"/>
+      <c r="D49" s="10" t="inlineStr">
+        <is>
+          <t>R4 - Recycling/Reclamation Of Metals</t>
+        </is>
+      </c>
+      <c r="E49" s="12">
+        <v>4.1</v>
+      </c>
+      <c r="F49" s="10">
+        <v>2966</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="10"/>
+      <c r="B50" s="11"/>
+      <c r="C50" s="11"/>
+      <c r="D50" s="10" t="inlineStr">
+        <is>
+          <t>D3 - Deep Injection</t>
+        </is>
+      </c>
+      <c r="E50" s="12">
+        <v>1.4</v>
+      </c>
+      <c r="F50" s="10">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="10"/>
+      <c r="B51" s="11"/>
+      <c r="C51" s="11"/>
+      <c r="D51" s="10" t="inlineStr">
+        <is>
+          <t>RC1</t>
+        </is>
+      </c>
+      <c r="E51" s="12">
+        <v>0.8</v>
+      </c>
+      <c r="F51" s="10">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="10"/>
+      <c r="B52" s="11"/>
+      <c r="C52" s="11"/>
+      <c r="D52" s="10" t="inlineStr">
+        <is>
+          <t>All Other (22)</t>
+        </is>
+      </c>
+      <c r="E52" s="12">
+        <v>2.5</v>
+      </c>
+      <c r="F52" s="10">
+        <v>1836</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">WS_WASTE_TYPE
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>Waste-stream type.</t>
+          </r>
+        </is>
+      </c>
+      <c r="B53" s="11" t="inlineStr">
+        <is>
+          <t>0.1%
+(40)</t>
+        </is>
+      </c>
+      <c r="C53" s="11">
+        <v>8</v>
+      </c>
+      <c r="D53" s="10" t="inlineStr">
+        <is>
+          <t>UNC</t>
+        </is>
+      </c>
+      <c r="E53" s="12">
+        <v>95.8</v>
+      </c>
+      <c r="F53" s="10">
+        <v>69225</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="10"/>
+      <c r="B54" s="11"/>
+      <c r="C54" s="11"/>
+      <c r="D54" s="10" t="inlineStr">
+        <is>
+          <t>HAZ - Hazardous Waste</t>
+        </is>
+      </c>
+      <c r="E54" s="12">
+        <v>3.4</v>
+      </c>
+      <c r="F54" s="10">
+        <v>2424</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="10"/>
+      <c r="B55" s="11"/>
+      <c r="C55" s="11"/>
+      <c r="D55" s="10" t="inlineStr">
+        <is>
+          <t>UNIV - Universal Waste</t>
+        </is>
+      </c>
+      <c r="E55" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="F55" s="10">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="10"/>
+      <c r="B56" s="11"/>
+      <c r="C56" s="11"/>
+      <c r="D56" s="10" t="inlineStr">
+        <is>
+          <t>SLABS - Spent Lead-Acid Batteries</t>
+        </is>
+      </c>
+      <c r="E56" s="12">
+        <v>0.1</v>
+      </c>
+      <c r="F56" s="10">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="10"/>
+      <c r="B57" s="11"/>
+      <c r="C57" s="11"/>
+      <c r="D57" s="10" t="inlineStr">
+        <is>
+          <t>MIXED - Mixed Waste</t>
+        </is>
+      </c>
+      <c r="E57" s="12">
+        <v>0</v>
+      </c>
+      <c r="F57" s="10">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="10"/>
+      <c r="B58" s="11"/>
+      <c r="C58" s="11"/>
+      <c r="D58" s="10" t="inlineStr">
+        <is>
+          <t>All Other (3)</t>
+        </is>
+      </c>
+      <c r="E58" s="12">
+        <v>0</v>
+      </c>
+      <c r="F58" s="10">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">HAZARD_CLASS
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>UN / DOT hazard class of the waste.</t>
+          </r>
+        </is>
+      </c>
+      <c r="B59" s="11" t="inlineStr">
+        <is>
+          <t>0.2%
+(156)</t>
+        </is>
+      </c>
+      <c r="C59" s="11">
+        <v>19</v>
+      </c>
+      <c r="D59" s="10" t="inlineStr">
+        <is>
+          <t>8 - Corrosive</t>
+        </is>
+      </c>
+      <c r="E59" s="12">
+        <v>21.7</v>
+      </c>
+      <c r="F59" s="10">
+        <v>15701</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="10"/>
+      <c r="B60" s="11"/>
+      <c r="C60" s="11"/>
+      <c r="D60" s="10" t="inlineStr">
+        <is>
+          <t>6.1 - Toxic</t>
+        </is>
+      </c>
+      <c r="E60" s="12">
+        <v>16.7</v>
+      </c>
+      <c r="F60" s="10">
+        <v>12059</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="10"/>
+      <c r="B61" s="11"/>
+      <c r="C61" s="11"/>
+      <c r="D61" s="10" t="inlineStr">
+        <is>
+          <t>3 - Flammable Liquid</t>
+        </is>
+      </c>
+      <c r="E61" s="12">
+        <v>14.6</v>
+      </c>
+      <c r="F61" s="10">
+        <v>10564</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="10"/>
+      <c r="B62" s="11"/>
+      <c r="C62" s="11"/>
+      <c r="D62" s="10" t="inlineStr">
+        <is>
+          <t>9 - Miscellaneous Dangerous Goods</t>
+        </is>
+      </c>
+      <c r="E62" s="12">
+        <v>6.8</v>
+      </c>
+      <c r="F62" s="10">
+        <v>4917</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="10"/>
+      <c r="B63" s="11"/>
+      <c r="C63" s="11"/>
+      <c r="D63" s="10" t="inlineStr">
+        <is>
+          <t>4.3 - Dangerous When Wet</t>
+        </is>
+      </c>
+      <c r="E63" s="12">
+        <v>6.3</v>
+      </c>
+      <c r="F63" s="10">
+        <v>4541</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="10"/>
+      <c r="B64" s="11"/>
+      <c r="C64" s="11"/>
+      <c r="D64" s="10" t="inlineStr">
+        <is>
+          <t>All Other (14)</t>
+        </is>
+      </c>
+      <c r="E64" s="12">
+        <v>33.6</v>
+      </c>
+      <c r="F64" s="10">
+        <v>24292</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">UN_ID_NUMBER
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>UN number identifying the substance for transport.</t>
+          </r>
+        </is>
+      </c>
+      <c r="B65" s="11" t="inlineStr">
+        <is>
+          <t>0.2%
+(156)</t>
+        </is>
+      </c>
+      <c r="C65" s="11">
+        <v>764</v>
+      </c>
+      <c r="D65" s="10" t="inlineStr">
+        <is>
+          <t>UN3077</t>
+        </is>
+      </c>
+      <c r="E65" s="12">
+        <v>3</v>
+      </c>
+      <c r="F65" s="10">
+        <v>2203</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="10"/>
+      <c r="B66" s="11"/>
+      <c r="C66" s="11"/>
+      <c r="D66" s="10" t="inlineStr">
+        <is>
+          <t>UN3082</t>
+        </is>
+      </c>
+      <c r="E66" s="12">
+        <v>2.1</v>
+      </c>
+      <c r="F66" s="10">
+        <v>1524</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="10"/>
+      <c r="B67" s="11"/>
+      <c r="C67" s="11"/>
+      <c r="D67" s="10" t="inlineStr">
+        <is>
+          <t>UN1993</t>
+        </is>
+      </c>
+      <c r="E67" s="12">
+        <v>1.6</v>
+      </c>
+      <c r="F67" s="10">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="10"/>
+      <c r="B68" s="11"/>
+      <c r="C68" s="11"/>
+      <c r="D68" s="10" t="inlineStr">
+        <is>
+          <t>UN3264</t>
+        </is>
+      </c>
+      <c r="E68" s="12">
+        <v>1.1</v>
+      </c>
+      <c r="F68" s="10">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="10"/>
+      <c r="B69" s="11"/>
+      <c r="C69" s="11"/>
+      <c r="D69" s="10" t="inlineStr">
+        <is>
+          <t>UN1760</t>
+        </is>
+      </c>
+      <c r="E69" s="12">
+        <v>0.9</v>
+      </c>
+      <c r="F69" s="10">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="10"/>
+      <c r="B70" s="11"/>
+      <c r="C70" s="11"/>
+      <c r="D70" s="10" t="inlineStr">
+        <is>
+          <t>All Other (759)</t>
+        </is>
+      </c>
+      <c r="E70" s="12">
+        <v>91</v>
+      </c>
+      <c r="F70" s="10">
+        <v>65704</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">BASEL_WASTE_CODES
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>Basel Convention waste codes on the stream (one row can list several).</t>
+          </r>
+        </is>
+      </c>
+      <c r="B71" s="11" t="inlineStr">
+        <is>
+          <t>0.1%
+(61)</t>
+        </is>
+      </c>
+      <c r="C71" s="11">
+        <v>181</v>
+      </c>
+      <c r="D71" s="10" t="inlineStr">
+        <is>
+          <t>A4140</t>
+        </is>
+      </c>
+      <c r="E71" s="12">
+        <v>26.2</v>
+      </c>
+      <c r="F71" s="10">
+        <v>18918</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="10"/>
+      <c r="B72" s="11"/>
+      <c r="C72" s="11"/>
+      <c r="D72" s="10" t="inlineStr">
+        <is>
+          <t>A4140; N/A</t>
+        </is>
+      </c>
+      <c r="E72" s="12">
+        <v>17.3</v>
+      </c>
+      <c r="F72" s="10">
+        <v>12527</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="10"/>
+      <c r="B73" s="11"/>
+      <c r="C73" s="11"/>
+      <c r="D73" s="10" t="inlineStr">
+        <is>
+          <t>A4090</t>
+        </is>
+      </c>
+      <c r="E73" s="12">
+        <v>8.9</v>
+      </c>
+      <c r="F73" s="10">
+        <v>6452</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="10"/>
+      <c r="B74" s="11"/>
+      <c r="C74" s="11"/>
+      <c r="D74" s="10" t="inlineStr">
+        <is>
+          <t>A4090; N/A</t>
+        </is>
+      </c>
+      <c r="E74" s="12">
+        <v>5.5</v>
+      </c>
+      <c r="F74" s="10">
+        <v>4007</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="10"/>
+      <c r="B75" s="11"/>
+      <c r="C75" s="11"/>
+      <c r="D75" s="10" t="inlineStr">
+        <is>
+          <t>A3140</t>
+        </is>
+      </c>
+      <c r="E75" s="12">
+        <v>3.5</v>
+      </c>
+      <c r="F75" s="10">
+        <v>2550</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="10"/>
+      <c r="B76" s="11"/>
+      <c r="C76" s="11"/>
+      <c r="D76" s="10" t="inlineStr">
+        <is>
+          <t>All Other (176)</t>
+        </is>
+      </c>
+      <c r="E76" s="12">
+        <v>38.4</v>
+      </c>
+      <c r="F76" s="10">
+        <v>27715</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">EPA_WASTE_CODES
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>RCRA waste codes on the stream (one row can list several).</t>
+          </r>
+        </is>
+      </c>
+      <c r="B77" s="11" t="inlineStr">
+        <is>
+          <t>95.6%
+(69024)</t>
+        </is>
+      </c>
+      <c r="C77" s="11">
+        <v>162</v>
+      </c>
+      <c r="D77" s="10" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="E77" s="12">
+        <v>0.7</v>
+      </c>
+      <c r="F77" s="10">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="10"/>
+      <c r="B78" s="11"/>
+      <c r="C78" s="11"/>
+      <c r="D78" s="10" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="E78" s="12">
+        <v>0.4</v>
+      </c>
+      <c r="F78" s="10">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="10"/>
+      <c r="B79" s="11"/>
+      <c r="C79" s="11"/>
+      <c r="D79" s="10" t="inlineStr">
+        <is>
+          <t>D002</t>
+        </is>
+      </c>
+      <c r="E79" s="12">
+        <v>0.4</v>
+      </c>
+      <c r="F79" s="10">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="10"/>
+      <c r="B80" s="11"/>
+      <c r="C80" s="11"/>
+      <c r="D80" s="10" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="E80" s="12">
+        <v>0.3</v>
+      </c>
+      <c r="F80" s="10">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="10"/>
+      <c r="B81" s="11"/>
+      <c r="C81" s="11"/>
+      <c r="D81" s="10" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="E81" s="12">
+        <v>0.2</v>
+      </c>
+      <c r="F81" s="10">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="10"/>
+      <c r="B82" s="11"/>
+      <c r="C82" s="11"/>
+      <c r="D82" s="10" t="inlineStr">
+        <is>
+          <t>All Other (157)</t>
+        </is>
+      </c>
+      <c r="E82" s="12">
+        <v>2.4</v>
+      </c>
+      <c r="F82" s="10">
+        <v>1761</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="14" t="inlineStr">
+        <is>
+          <t>Notes on missing values:
+CONSENT_UOM / CONSENT_FREQUENCY: Not applicable. Blank for notices that were objected to or withdrawn rather than consented.
+INTERIM_COUNTRY / INTERIM_OPERATIONS: Not applicable. Most shipments go straight to the final facility.
+EPA_WASTE_CODES: Not applicable. Imported streams are described by Basel codes, and few carry a RCRA code as well.</t>
+        </is>
+      </c>
+      <c r="B84" s="14"/>
+      <c r="C84" s="14"/>
+      <c r="D84" s="14"/>
+      <c r="E84" s="14"/>
+      <c r="F84" s="14"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="14"/>
+      <c r="B85" s="14"/>
+      <c r="C85" s="14"/>
+      <c r="D85" s="14"/>
+      <c r="E85" s="14"/>
+      <c r="F85" s="14"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="14"/>
+      <c r="B86" s="14"/>
+      <c r="C86" s="14"/>
+      <c r="D86" s="14"/>
+      <c r="E86" s="14"/>
+      <c r="F86" s="14"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="14"/>
+      <c r="B87" s="14"/>
+      <c r="C87" s="14"/>
+      <c r="D87" s="14"/>
+      <c r="E87" s="14"/>
+      <c r="F87" s="14"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="14" t="inlineStr">
         <is>
           <t>Variables dropped (present in the source file but not summarized):
-'NOTICE_ID', 'NOTICE_TYPE', 'NOTICE_PROGRESS', 'EXPORTER_NAME',
-'EXPORTER_FOREIGN_ID', 'EXPORTER_ADDRESS', 'IMPORTER_NAME',
-'IMPORTER_ADDRESS', 'SHIPPER_NAME', 'SHIPPER_EPA_ID', 'SHIPPER_FOREIGN_ID',
-'SHIPPER_ADDRESS', 'SHIPPER_COUNTRY', 'INTERIM_NAME', 'INTERIM_EPA_ID',
-'INTERIM_FOREIGN_ID', 'INTERIM_ADDRESS', 'INTERIM_COUNTRY',
-'INTERIM_OPERATIONS', 'FINAL_NAME', 'FINAL_EPA_ID', 'FINAL_FOREIGN_ID',
-'FINAL_ADDRESS', 'CONSENT_NUMBER', 'CONSENT_UOM', 'WASTE_STREAM_NUMBER',
-'WASTE_DESCRIPTION', 'UN_ID_NUMBER', 'BASEL_WASTE_CODES', 'EPA_WASTE_CODES'</t>
-        </is>
-      </c>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="14"/>
-      <c r="B49" s="14"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="14"/>
-      <c r="B50" s="14"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="14"/>
-      <c r="B51" s="14"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="14"/>
-      <c r="B52" s="14"/>
-      <c r="C52" s="14"/>
-      <c r="D52" s="14"/>
-      <c r="E52" s="14"/>
-      <c r="F52" s="14"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="14"/>
-      <c r="B53" s="14"/>
-      <c r="C53" s="14"/>
-      <c r="D53" s="14"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="14"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="14"/>
-      <c r="B54" s="14"/>
-      <c r="C54" s="14"/>
-      <c r="D54" s="14"/>
-      <c r="E54" s="14"/>
-      <c r="F54" s="14"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="14"/>
-      <c r="B55" s="14"/>
-      <c r="C55" s="14"/>
-      <c r="D55" s="14"/>
-      <c r="E55" s="14"/>
-      <c r="F55" s="14"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="14"/>
-      <c r="B56" s="14"/>
-      <c r="C56" s="14"/>
-      <c r="D56" s="14"/>
-      <c r="E56" s="14"/>
-      <c r="F56" s="14"/>
+'NOTICE_ID', 'CONSENT_NUMBER', 'IMPORTER_NAME', 'IMPORTER_ADDRESS',
+'EXPORTER_NAME', 'EXPORTER_FOREIGN_ID', 'EXPORTER_ADDRESS', 'SHIPPER_NAME',
+'SHIPPER_EPA_ID', 'SHIPPER_FOREIGN_ID', 'SHIPPER_ADDRESS', 'INTERIM_NAME',
+'INTERIM_EPA_ID', 'INTERIM_FOREIGN_ID', 'INTERIM_ADDRESS', 'FINAL_NAME',
+'FINAL_EPA_ID', 'FINAL_FOREIGN_ID', 'FINAL_ADDRESS', 'WASTE_DESCRIPTION'</t>
+        </is>
+      </c>
+      <c r="B89" s="14"/>
+      <c r="C89" s="14"/>
+      <c r="D89" s="14"/>
+      <c r="E89" s="14"/>
+      <c r="F89" s="14"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="14"/>
+      <c r="B90" s="14"/>
+      <c r="C90" s="14"/>
+      <c r="D90" s="14"/>
+      <c r="E90" s="14"/>
+      <c r="F90" s="14"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="14"/>
+      <c r="B91" s="14"/>
+      <c r="C91" s="14"/>
+      <c r="D91" s="14"/>
+      <c r="E91" s="14"/>
+      <c r="F91" s="14"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="14"/>
+      <c r="B92" s="14"/>
+      <c r="C92" s="14"/>
+      <c r="D92" s="14"/>
+      <c r="E92" s="14"/>
+      <c r="F92" s="14"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="14"/>
+      <c r="B93" s="14"/>
+      <c r="C93" s="14"/>
+      <c r="D93" s="14"/>
+      <c r="E93" s="14"/>
+      <c r="F93" s="14"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="14"/>
+      <c r="B94" s="14"/>
+      <c r="C94" s="14"/>
+      <c r="D94" s="14"/>
+      <c r="E94" s="14"/>
+      <c r="F94" s="14"/>
     </row>
   </sheetData>
-  <mergeCells count="30">
+  <mergeCells count="49">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="D3:F4"/>
     <mergeCell ref="B5:F5"/>
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="C7:C9"/>
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="C10:C13"/>
-    <mergeCell ref="A14:A19"/>
-    <mergeCell ref="B14:B19"/>
-    <mergeCell ref="C14:C19"/>
-    <mergeCell ref="A20:A25"/>
-    <mergeCell ref="B20:B25"/>
-    <mergeCell ref="C20:C25"/>
-    <mergeCell ref="A26:A31"/>
-    <mergeCell ref="B26:B31"/>
-    <mergeCell ref="C26:C31"/>
-    <mergeCell ref="A32:A37"/>
-    <mergeCell ref="B32:B37"/>
-    <mergeCell ref="C32:C37"/>
-    <mergeCell ref="A38:A43"/>
-    <mergeCell ref="B38:B43"/>
-    <mergeCell ref="C38:C43"/>
-    <mergeCell ref="A44:A46"/>
-    <mergeCell ref="B44:B46"/>
-    <mergeCell ref="C44:C46"/>
-    <mergeCell ref="A48:F56"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="B12:B15"/>
+    <mergeCell ref="C12:C15"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="B16:B18"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="C19:C21"/>
+    <mergeCell ref="A22:A27"/>
+    <mergeCell ref="B22:B27"/>
+    <mergeCell ref="C22:C27"/>
+    <mergeCell ref="A28:A33"/>
+    <mergeCell ref="B28:B33"/>
+    <mergeCell ref="C28:C33"/>
+    <mergeCell ref="A35:A40"/>
+    <mergeCell ref="B35:B40"/>
+    <mergeCell ref="C35:C40"/>
+    <mergeCell ref="A41:A46"/>
+    <mergeCell ref="B41:B46"/>
+    <mergeCell ref="C41:C46"/>
+    <mergeCell ref="A47:A52"/>
+    <mergeCell ref="B47:B52"/>
+    <mergeCell ref="C47:C52"/>
+    <mergeCell ref="A53:A58"/>
+    <mergeCell ref="B53:B58"/>
+    <mergeCell ref="C53:C58"/>
+    <mergeCell ref="A59:A64"/>
+    <mergeCell ref="B59:B64"/>
+    <mergeCell ref="C59:C64"/>
+    <mergeCell ref="A65:A70"/>
+    <mergeCell ref="B65:B70"/>
+    <mergeCell ref="C65:C70"/>
+    <mergeCell ref="A71:A76"/>
+    <mergeCell ref="B71:B76"/>
+    <mergeCell ref="C71:C76"/>
+    <mergeCell ref="A77:A82"/>
+    <mergeCell ref="B77:B82"/>
+    <mergeCell ref="C77:C82"/>
+    <mergeCell ref="A84:F87"/>
+    <mergeCell ref="A89:F94"/>
   </mergeCells>
   <printOptions gridLines="1" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1554,7 +2404,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="23"/>
@@ -1701,32 +2551,32 @@
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>CONSENT_QUANTITY</t>
+          <t>WASTE_STREAM_NUMBER</t>
         </is>
       </c>
       <c r="B6" s="10">
-        <v>71257</v>
+        <v>72190</v>
       </c>
       <c r="C6" s="10">
-        <v>1.3</v>
+        <v>0.1</v>
       </c>
       <c r="D6" s="10">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="E6" s="10">
-        <v>20000</v>
+        <v>1</v>
       </c>
       <c r="F6" s="10">
-        <v>2500000</v>
+        <v>427</v>
       </c>
       <c r="G6" s="10">
-        <v>521070000</v>
+        <v>490</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>CONSENT_SHIPMENTS</t>
+          <t>CONSENT_QUANTITY</t>
         </is>
       </c>
       <c r="B7" s="10">
@@ -1736,19 +2586,70 @@
         <v>1.3</v>
       </c>
       <c r="D7" s="10">
+        <v>0.1</v>
+      </c>
+      <c r="E7" s="10">
+        <v>20000</v>
+      </c>
+      <c r="F7" s="10">
+        <v>2500000</v>
+      </c>
+      <c r="G7" s="10">
+        <v>521070000</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>CONSENT_SHIPMENTS</t>
+        </is>
+      </c>
+      <c r="B8" s="10">
+        <v>71257</v>
+      </c>
+      <c r="C8" s="10">
+        <v>1.3</v>
+      </c>
+      <c r="D8" s="10">
         <v>1</v>
       </c>
-      <c r="E7" s="10">
+      <c r="E8" s="10">
         <v>50</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F8" s="10">
         <v>250</v>
       </c>
-      <c r="G7" s="10">
+      <c r="G8" s="10">
         <v>80000</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>Notes on missing values:
+CONSENT_START_DATE / CONSENT_END_DATE / CONSENT_QUANTITY / CONSENT_SHIPMENTS: Not applicable. Blank for notices that were objected to or withdrawn rather than consented.</t>
+        </is>
+      </c>
+      <c r="B10" s="14"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="14"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="14"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A10:G11"/>
+  </mergeCells>
   <printOptions gridLines="1" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
